--- a/Practical-29June.xlsx
+++ b/Practical-29June.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F434A7EE-2604-4A1C-9F64-4CB8264EA7C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Employee_Data" sheetId="1" r:id="rId1"/>
@@ -352,7 +352,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1" indent="1"/>
@@ -388,16 +388,15 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -934,7 +933,7 @@
       <c r="A24" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="B24" s="18">
+      <c r="B24" s="13">
         <f>VLOOKUP(A24, B2:E9, 4, FALSE)</f>
         <v>58000</v>
       </c>
@@ -970,7 +969,7 @@
       <c r="A33" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="B33" s="19" t="s">
+      <c r="B33" s="18" t="s">
         <v>1</v>
       </c>
     </row>
@@ -1067,10 +1066,10 @@
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="19" t="s">
+      <c r="A6" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="B6" s="19" t="s">
+      <c r="B6" s="18" t="s">
         <v>33</v>
       </c>
     </row>
@@ -1078,7 +1077,7 @@
       <c r="A7" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="B7" s="20">
+      <c r="B7" s="19">
         <f xml:space="preserve"> HLOOKUP(A7,A1:F2,2,0)</f>
         <v>0.12</v>
       </c>
@@ -1089,10 +1088,10 @@
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="19" t="s">
+      <c r="A11" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="B11" s="19" t="s">
+      <c r="B11" s="18" t="s">
         <v>33</v>
       </c>
     </row>
@@ -1100,7 +1099,7 @@
       <c r="A12" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="B12" s="20">
+      <c r="B12" s="19">
         <f xml:space="preserve"> HLOOKUP(A12,A1:F2,2,0)</f>
         <v>0.15</v>
       </c>
@@ -1111,19 +1110,19 @@
       </c>
     </row>
     <row r="16" spans="1:6" ht="15" x14ac:dyDescent="0.35">
-      <c r="A16" s="19" t="s">
+      <c r="A16" s="18" t="s">
         <v>44</v>
       </c>
-      <c r="B16" s="19" t="s">
+      <c r="B16" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="C16" s="19" t="s">
+      <c r="C16" s="18" t="s">
         <v>33</v>
       </c>
       <c r="D16" s="14" t="s">
         <v>43</v>
       </c>
-      <c r="E16" s="21" t="s">
+      <c r="E16" s="20" t="s">
         <v>2</v>
       </c>
     </row>
@@ -1154,10 +1153,10 @@
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A21" s="19" t="s">
+      <c r="A21" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="B21" s="19" t="s">
+      <c r="B21" s="18" t="s">
         <v>47</v>
       </c>
     </row>
@@ -1204,7 +1203,7 @@
       <c r="A4" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="19" t="s">
+      <c r="B4" s="18" t="s">
         <v>4</v>
       </c>
       <c r="D4" t="s">
@@ -1221,10 +1220,10 @@
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A7" s="19" t="s">
+      <c r="A7" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="B7" s="19" t="s">
+      <c r="B7" s="18" t="s">
         <v>2</v>
       </c>
       <c r="D7" t="s">
@@ -1241,10 +1240,10 @@
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10" s="19" t="s">
+      <c r="A10" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="B10" s="19" t="s">
+      <c r="B10" s="18" t="s">
         <v>3</v>
       </c>
       <c r="D10" t="s">
@@ -1270,7 +1269,7 @@
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A14" s="22" t="s">
+      <c r="A14" s="21" t="s">
         <v>51</v>
       </c>
       <c r="B14" s="13" t="str">
@@ -1279,10 +1278,10 @@
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A16" s="19" t="s">
+      <c r="A16" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="B16" s="19" t="s">
+      <c r="B16" s="18" t="s">
         <v>33</v>
       </c>
       <c r="D16" t="s">
